--- a/docs/Mapping_casi_uso/cittadinanza/Citt_027.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_027.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="157">
   <si>
     <t>Sezione</t>
   </si>
@@ -314,81 +314,111 @@
     <t>flagFirmatario</t>
   </si>
   <si>
+    <t>Dati accertamento</t>
+  </si>
+  <si>
+    <t>Data accertamento</t>
+  </si>
+  <si>
+    <t>evento.enteDichiarante</t>
+  </si>
+  <si>
+    <t>dataTrascrizione</t>
+  </si>
+  <si>
+    <t>Numero accertamento</t>
+  </si>
+  <si>
+    <t>estremiDocumento</t>
+  </si>
+  <si>
+    <t>Atto collegato di Cittadinanza</t>
+  </si>
+  <si>
+    <t>Id atto</t>
+  </si>
+  <si>
+    <t>evento.eventoCollegatoCittadinanza</t>
+  </si>
+  <si>
+    <t>idAnsc</t>
+  </si>
+  <si>
+    <t>opzionale</t>
+  </si>
+  <si>
+    <t>Provincia registrazione</t>
+  </si>
+  <si>
+    <t>idProvinciaRegistrazione</t>
+  </si>
+  <si>
+    <t>Provincia registrazione - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaRegistrazione</t>
+  </si>
+  <si>
+    <t>Comune registrazione</t>
+  </si>
+  <si>
+    <t>idComuneRegistrazione</t>
+  </si>
+  <si>
+    <t>Comune registrazione - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneRegistrazione</t>
+  </si>
+  <si>
+    <t>Tipo evento</t>
+  </si>
+  <si>
+    <t>idtipocontenuto</t>
+  </si>
+  <si>
+    <t>Numero Comunale</t>
+  </si>
+  <si>
+    <t>Anno atto</t>
+  </si>
+  <si>
+    <t>annoAtto</t>
+  </si>
+  <si>
+    <t>Data atto</t>
+  </si>
+  <si>
+    <t>Parte</t>
+  </si>
+  <si>
+    <t>parte</t>
+  </si>
+  <si>
+    <t>Serie</t>
+  </si>
+  <si>
+    <t>serie</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>Tipo registro</t>
+  </si>
+  <si>
+    <t>tipologia</t>
+  </si>
+  <si>
     <t>Atto nascita intestatario</t>
   </si>
   <si>
-    <t>Provincia registrazione</t>
-  </si>
-  <si>
     <t>evento.eventoCollegato</t>
   </si>
   <si>
-    <t>idProvinciaRegistrazione</t>
-  </si>
-  <si>
-    <t>opzionale</t>
-  </si>
-  <si>
-    <t>Provincia registrazione - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaRegistrazione</t>
-  </si>
-  <si>
-    <t>Comune registrazione</t>
-  </si>
-  <si>
-    <t>idComuneRegistrazione</t>
-  </si>
-  <si>
-    <t>Comune registrazione - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneRegistrazione</t>
-  </si>
-  <si>
-    <t>Tipo evento</t>
-  </si>
-  <si>
-    <t>idtipocontenuto</t>
-  </si>
-  <si>
-    <t>Numero Comunale</t>
-  </si>
-  <si>
-    <t>Anno atto</t>
-  </si>
-  <si>
-    <t>annoAtto</t>
-  </si>
-  <si>
-    <t>Data atto</t>
-  </si>
-  <si>
-    <t>Parte</t>
-  </si>
-  <si>
-    <t>parte</t>
-  </si>
-  <si>
-    <t>Serie</t>
-  </si>
-  <si>
-    <t>serie</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>volume</t>
-  </si>
-  <si>
-    <t>Tipo registro</t>
-  </si>
-  <si>
-    <t>tipologia</t>
-  </si>
-  <si>
     <t>Autorità mittente</t>
   </si>
   <si>
@@ -398,13 +428,7 @@
     <t>evento.trascrizioneCittadinanza.atto.enteEstero</t>
   </si>
   <si>
-    <t>dataTrascrizione</t>
-  </si>
-  <si>
     <t>Estremi documento</t>
-  </si>
-  <si>
-    <t>estremiDocumento</t>
   </si>
   <si>
     <t>Nome ente</t>
@@ -517,10 +541,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="43.9609375" customWidth="true" bestFit="true"/>
@@ -1526,7 +1550,7 @@
         <v>101</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>102</v>
@@ -1538,7 +1562,7 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -1546,27 +1570,27 @@
         <v>100</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>102</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>107</v>
@@ -1575,237 +1599,237 @@
         <v>33</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>128</v>
@@ -1814,21 +1838,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>130</v>
@@ -1837,21 +1861,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>132</v>
@@ -1860,190 +1884,535 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C67" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="C77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" s="2" t="s">
+      <c r="F77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>18</v>
       </c>
     </row>
